--- a/practice.excel.xlsx
+++ b/practice.excel.xlsx
@@ -8,14 +8,28 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\excel.xml\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A7414F6-2FD6-4D7C-A65B-129058EFE5D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FC76A51-6FB7-4BAF-9162-08F3D4D5B315}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2DD6822B-C6FC-4C62-BBE7-0C6B23F82B42}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="9" activeTab="10" xr2:uid="{2DD6822B-C6FC-4C62-BBE7-0C6B23F82B42}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="full-pivote" sheetId="3" r:id="rId1"/>
+    <sheet name="ind1" sheetId="4" r:id="rId2"/>
+    <sheet name="ind2" sheetId="5" r:id="rId3"/>
+    <sheet name="Sheet9" sheetId="9" r:id="rId4"/>
+    <sheet name="Sheet10" sheetId="10" r:id="rId5"/>
+    <sheet name="Sheet11" sheetId="12" r:id="rId6"/>
+    <sheet name="Sheet13" sheetId="13" r:id="rId7"/>
+    <sheet name="Sheet14" sheetId="14" r:id="rId8"/>
+    <sheet name="Sheet15" sheetId="15" r:id="rId9"/>
+    <sheet name="Sheet16" sheetId="16" r:id="rId10"/>
+    <sheet name="Sheet4" sheetId="19" r:id="rId11"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="1" r:id="rId13"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -34,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="179">
   <si>
     <t xml:space="preserve">        Name</t>
   </si>
@@ -455,12 +469,150 @@
   <si>
     <t>t stacked bar and 100% stacked bar</t>
   </si>
+  <si>
+    <t xml:space="preserve">  Ram</t>
+  </si>
+  <si>
+    <t>hanuman</t>
+  </si>
+  <si>
+    <t>lakshman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Pivote Tables</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Salesperson</t>
+  </si>
+  <si>
+    <t>Region</t>
+  </si>
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Units Sold</t>
+  </si>
+  <si>
+    <t>Unit Price</t>
+  </si>
+  <si>
+    <t>Total Sales</t>
+  </si>
+  <si>
+    <t>Ravi</t>
+  </si>
+  <si>
+    <t>South</t>
+  </si>
+  <si>
+    <t>Laptop</t>
+  </si>
+  <si>
+    <t>Electronics</t>
+  </si>
+  <si>
+    <t>Priya</t>
+  </si>
+  <si>
+    <t>North</t>
+  </si>
+  <si>
+    <t>Mouse</t>
+  </si>
+  <si>
+    <t>Accessories</t>
+  </si>
+  <si>
+    <t>Arun</t>
+  </si>
+  <si>
+    <t>East</t>
+  </si>
+  <si>
+    <t>Keyboard</t>
+  </si>
+  <si>
+    <t>Sneha</t>
+  </si>
+  <si>
+    <t>West</t>
+  </si>
+  <si>
+    <t>Mobile</t>
+  </si>
+  <si>
+    <t>Headphones</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Column Labels</t>
+  </si>
+  <si>
+    <t>Sum of Total Sales</t>
+  </si>
+  <si>
+    <t>(All)</t>
+  </si>
+  <si>
+    <t>Sum of Units Sold</t>
+  </si>
+  <si>
+    <t>1.Region-wise product sales</t>
+  </si>
+  <si>
+    <t>2.Year-wise department profit</t>
+  </si>
+  <si>
+    <t>Max of Total Sales</t>
+  </si>
+  <si>
+    <t>2.Product-wise Units Sold</t>
+  </si>
+  <si>
+    <t>3.Region-wise Maximum Sales</t>
+  </si>
+  <si>
+    <t>4.Salesperson-wise Total Sales</t>
+  </si>
+  <si>
+    <t>5.Salesperson-wise Product Units Sold</t>
+  </si>
+  <si>
+    <t>Average of Unit Price</t>
+  </si>
+  <si>
+    <t>Show only South region Laptop sales</t>
+  </si>
+  <si>
+    <t>Setup:</t>
+  </si>
+  <si>
+    <t>Filters → Region</t>
+  </si>
+  <si>
+    <t>Filters → Product</t>
+  </si>
+  <si>
+    <t>Values → Total Sales</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -481,16 +633,57 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="9" tint="0.39997558519241921"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -498,19 +691,176 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFABABAB"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFABABAB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="65"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFABABAB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="65"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFABABAB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFABABAB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFABABAB"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="65"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="65"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="65"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="65"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFABABAB"/>
+      </right>
+      <top style="thin">
+        <color indexed="65"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFABABAB"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="65"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFABABAB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="65"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="65"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFABABAB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="65"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFABABAB"/>
+      </right>
+      <top style="thin">
+        <color indexed="65"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFABABAB"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="23">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -630,6 +980,53 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="21" formatCode="dd/mmm"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="21" formatCode="dd/mmm"/>
@@ -961,6 +1358,2182 @@
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="accent1"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:radarChart>
+        <c:radarStyle val="filled"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$B$196</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>HP</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent1">
+                    <a:satMod val="103000"/>
+                    <a:lumMod val="102000"/>
+                    <a:tint val="94000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="50000">
+                  <a:schemeClr val="accent1">
+                    <a:satMod val="110000"/>
+                    <a:lumMod val="100000"/>
+                    <a:shade val="100000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="99000"/>
+                    <a:satMod val="120000"/>
+                    <a:shade val="78000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$197:$A$199</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>  Ram</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>hanuman</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>lakshman</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$197:$B$199</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>44</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-279C-4B5B-9979-C1B573DFDB75}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$196</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Attack</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent2">
+                    <a:satMod val="103000"/>
+                    <a:lumMod val="102000"/>
+                    <a:tint val="94000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="50000">
+                  <a:schemeClr val="accent2">
+                    <a:satMod val="110000"/>
+                    <a:lumMod val="100000"/>
+                    <a:shade val="100000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="99000"/>
+                    <a:satMod val="120000"/>
+                    <a:shade val="78000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$197:$A$199</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>  Ram</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>hanuman</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>lakshman</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$197:$C$199</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>49</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>52</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>48</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-279C-4B5B-9979-C1B573DFDB75}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$D$196</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Defense</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent3">
+                    <a:satMod val="103000"/>
+                    <a:lumMod val="102000"/>
+                    <a:tint val="94000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="50000">
+                  <a:schemeClr val="accent3">
+                    <a:satMod val="110000"/>
+                    <a:lumMod val="100000"/>
+                    <a:shade val="100000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent3">
+                    <a:lumMod val="99000"/>
+                    <a:satMod val="120000"/>
+                    <a:shade val="78000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$197:$A$199</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>  Ram</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>hanuman</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>lakshman</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$197:$D$199</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>49</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>65</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-279C-4B5B-9979-C1B573DFDB75}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$E$196</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Sp. Atk</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent4">
+                    <a:satMod val="103000"/>
+                    <a:lumMod val="102000"/>
+                    <a:tint val="94000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="50000">
+                  <a:schemeClr val="accent4">
+                    <a:satMod val="110000"/>
+                    <a:lumMod val="100000"/>
+                    <a:shade val="100000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent4">
+                    <a:lumMod val="99000"/>
+                    <a:satMod val="120000"/>
+                    <a:shade val="78000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$197:$A$199</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>  Ram</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>hanuman</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>lakshman</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$E$197:$E$199</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>50</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-279C-4B5B-9979-C1B573DFDB75}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$F$196</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Sp. Def</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent5">
+                    <a:satMod val="103000"/>
+                    <a:lumMod val="102000"/>
+                    <a:tint val="94000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="50000">
+                  <a:schemeClr val="accent5">
+                    <a:satMod val="110000"/>
+                    <a:lumMod val="100000"/>
+                    <a:shade val="100000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent5">
+                    <a:lumMod val="99000"/>
+                    <a:satMod val="120000"/>
+                    <a:shade val="78000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$197:$A$199</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>  Ram</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>hanuman</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>lakshman</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$F$197:$F$199</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>64</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-279C-4B5B-9979-C1B573DFDB75}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$G$196</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Speed</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent6">
+                    <a:satMod val="103000"/>
+                    <a:lumMod val="102000"/>
+                    <a:tint val="94000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="50000">
+                  <a:schemeClr val="accent6">
+                    <a:satMod val="110000"/>
+                    <a:lumMod val="100000"/>
+                    <a:shade val="100000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent6">
+                    <a:lumMod val="99000"/>
+                    <a:satMod val="120000"/>
+                    <a:shade val="78000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$197:$A$199</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>  Ram</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>hanuman</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>lakshman</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$G$197:$G$199</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>43</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-279C-4B5B-9979-C1B573DFDB75}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="121480975"/>
+        <c:axId val="121476655"/>
+      </c:radarChart>
+      <c:catAx>
+        <c:axId val="121480975"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:lumMod val="95000"/>
+                <a:alpha val="54000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="121476655"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="121476655"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
+                  <a:alpha val="10000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="121480975"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:gradFill flip="none" rotWithShape="1">
+      <a:gsLst>
+        <a:gs pos="0">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:gs>
+        <a:gs pos="100000">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="85000"/>
+            <a:lumOff val="15000"/>
+          </a:schemeClr>
+        </a:gs>
+      </a:gsLst>
+      <a:path path="circle">
+        <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+      </a:path>
+      <a:tileRect/>
+    </a:gradFill>
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:radarChart>
+        <c:radarStyle val="marker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$B$196</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>HP</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$197:$A$199</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>  Ram</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>hanuman</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>lakshman</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$197:$B$199</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>44</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1041-41F8-8213-CFB2A030BF1F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$196</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Attack</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$197:$A$199</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>  Ram</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>hanuman</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>lakshman</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$197:$C$199</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>49</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>52</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>48</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-1041-41F8-8213-CFB2A030BF1F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$D$196</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Defense</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$197:$A$199</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>  Ram</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>hanuman</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>lakshman</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$197:$D$199</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>49</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>65</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-1041-41F8-8213-CFB2A030BF1F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$E$196</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Sp. Atk</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$197:$A$199</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>  Ram</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>hanuman</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>lakshman</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$E$197:$E$199</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>50</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-1041-41F8-8213-CFB2A030BF1F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$F$196</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Sp. Def</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent5"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$197:$A$199</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>  Ram</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>hanuman</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>lakshman</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$F$197:$F$199</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>64</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-1041-41F8-8213-CFB2A030BF1F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$G$196</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Speed</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent6"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$197:$A$199</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>  Ram</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>hanuman</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>lakshman</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$G$197:$G$199</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>43</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-1041-41F8-8213-CFB2A030BF1F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="203866783"/>
+        <c:axId val="203856703"/>
+      </c:radarChart>
+      <c:catAx>
+        <c:axId val="203866783"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="203856703"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="203856703"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="203866783"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:radarChart>
+        <c:radarStyle val="filled"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$B$196</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>HP</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$197:$A$199</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>  Ram</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>hanuman</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>lakshman</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$197:$B$199</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>44</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-9405-47B6-9333-534928453CB4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$196</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Attack</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$197:$A$199</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>  Ram</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>hanuman</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>lakshman</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$197:$C$199</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>49</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>52</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>48</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-9405-47B6-9333-534928453CB4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$D$196</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Defense</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$197:$A$199</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>  Ram</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>hanuman</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>lakshman</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$197:$D$199</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>49</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>65</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-9405-47B6-9333-534928453CB4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$E$196</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Sp. Atk</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$197:$A$199</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>  Ram</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>hanuman</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>lakshman</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$E$197:$E$199</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>50</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-9405-47B6-9333-534928453CB4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$F$196</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Sp. Def</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent5"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$197:$A$199</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>  Ram</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>hanuman</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>lakshman</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$F$197:$F$199</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>64</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-9405-47B6-9333-534928453CB4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$G$196</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Speed</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent6"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$197:$A$199</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>  Ram</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>hanuman</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>lakshman</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$G$197:$G$199</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>43</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-9405-47B6-9333-534928453CB4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="203862943"/>
+        <c:axId val="203861503"/>
+      </c:radarChart>
+      <c:catAx>
+        <c:axId val="203862943"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="203861503"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="203861503"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="203862943"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
       </a:solidFill>
       <a:round/>
     </a:ln>
@@ -4612,6 +7185,126 @@
 </file>
 
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors10.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors11.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors12.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -5500,6 +8193,1507 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style10.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="321">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200" cap="all"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="85000"/>
+              <a:lumOff val="15000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+        </a:path>
+        <a:tileRect/>
+      </a:gradFill>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="15000"/>
+        <a:lumOff val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="34925" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="10000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="5000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="1" kern="1200" cap="none" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style11.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="317">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style12.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="317">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
   <cs:axisTitle>
@@ -9876,7 +14070,1294 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>533566</xdr:colOff>
+      <xdr:row>194</xdr:row>
+      <xdr:rowOff>160508</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>265375</xdr:colOff>
+      <xdr:row>210</xdr:row>
+      <xdr:rowOff>78790</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="11" name="Chart 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DCE932B3-1739-21E8-083D-95D4F894E12E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId10"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>25097</xdr:colOff>
+      <xdr:row>199</xdr:row>
+      <xdr:rowOff>15680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>20226</xdr:colOff>
+      <xdr:row>212</xdr:row>
+      <xdr:rowOff>161205</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="13" name="Chart 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1B9626C9-06E7-8973-F0C5-2A27E19D855C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>25399</xdr:colOff>
+      <xdr:row>199</xdr:row>
+      <xdr:rowOff>59266</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>516466</xdr:colOff>
+      <xdr:row>213</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="14" name="Chart 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BCF2BFB1-893B-2EFB-0E2E-73DF6A8171B8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId12"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="DELL" refreshedDate="46164.715273263886" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="15" xr:uid="{C10B3795-695A-4CB6-A978-FFFB6D8FA9BD}">
+  <cacheSource type="worksheet">
+    <worksheetSource name="Table16"/>
+  </cacheSource>
+  <cacheFields count="8">
+    <cacheField name="Date" numFmtId="16">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-01-01T00:00:00" maxDate="2026-01-16T00:00:00" count="15">
+        <d v="2026-01-01T00:00:00"/>
+        <d v="2026-01-02T00:00:00"/>
+        <d v="2026-01-03T00:00:00"/>
+        <d v="2026-01-04T00:00:00"/>
+        <d v="2026-01-05T00:00:00"/>
+        <d v="2026-01-06T00:00:00"/>
+        <d v="2026-01-07T00:00:00"/>
+        <d v="2026-01-08T00:00:00"/>
+        <d v="2026-01-09T00:00:00"/>
+        <d v="2026-01-10T00:00:00"/>
+        <d v="2026-01-11T00:00:00"/>
+        <d v="2026-01-12T00:00:00"/>
+        <d v="2026-01-13T00:00:00"/>
+        <d v="2026-01-14T00:00:00"/>
+        <d v="2026-01-15T00:00:00"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Salesperson" numFmtId="0">
+      <sharedItems count="4">
+        <s v="Ravi"/>
+        <s v="Priya"/>
+        <s v="Arun"/>
+        <s v="Sneha"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Region" numFmtId="0">
+      <sharedItems count="4">
+        <s v="South"/>
+        <s v="North"/>
+        <s v="East"/>
+        <s v="West"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Product" numFmtId="0">
+      <sharedItems count="5">
+        <s v="Laptop"/>
+        <s v="Mouse"/>
+        <s v="Keyboard"/>
+        <s v="Mobile"/>
+        <s v="Headphones"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Category" numFmtId="0">
+      <sharedItems count="2">
+        <s v="Electronics"/>
+        <s v="Accessories"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Units Sold" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="20"/>
+    </cacheField>
+    <cacheField name="Unit Price" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="400" maxValue="52000"/>
+    </cacheField>
+    <cacheField name="Total Sales" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="3900" maxValue="100000" count="15">
+        <n v="100000"/>
+        <n v="5000"/>
+        <n v="6000"/>
+        <n v="60000"/>
+        <n v="10500"/>
+        <n v="52000"/>
+        <n v="36000"/>
+        <n v="6750"/>
+        <n v="4400"/>
+        <n v="9600"/>
+        <n v="51000"/>
+        <n v="84000"/>
+        <n v="8000"/>
+        <n v="3900"/>
+        <n v="11200"/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="15">
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="2"/>
+    <n v="50000"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="10"/>
+    <n v="500"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="5"/>
+    <n v="1200"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="3"/>
+    <x v="3"/>
+    <x v="3"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="20000"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="4"/>
+    <x v="1"/>
+    <n v="7"/>
+    <n v="1500"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="1"/>
+    <n v="52000"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="3"/>
+    <x v="0"/>
+    <n v="2"/>
+    <n v="18000"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="3"/>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="15"/>
+    <n v="450"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="4"/>
+    <n v="1100"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="4"/>
+    <x v="1"/>
+    <n v="6"/>
+    <n v="1600"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="1"/>
+    <n v="51000"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="3"/>
+    <x v="3"/>
+    <x v="3"/>
+    <x v="0"/>
+    <n v="4"/>
+    <n v="21000"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <x v="12"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="20"/>
+    <n v="400"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="13"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="3"/>
+    <n v="1300"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="14"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="4"/>
+    <x v="1"/>
+    <n v="8"/>
+    <n v="1400"/>
+    <x v="14"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CB1309BF-1661-47CF-9276-E68AC77BBAF1}" name="PivotTable2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A4:C51" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="8">
+    <pivotField numFmtId="16" showAll="0"/>
+    <pivotField axis="axisRow" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="5">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="6">
+        <item x="4"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0">
+      <items count="16">
+        <item x="13"/>
+        <item x="8"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="7"/>
+        <item x="12"/>
+        <item x="9"/>
+        <item x="4"/>
+        <item x="14"/>
+        <item x="6"/>
+        <item x="10"/>
+        <item x="5"/>
+        <item x="3"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="4">
+    <field x="2"/>
+    <field x="3"/>
+    <field x="1"/>
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="47">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="2">
+      <x/>
+    </i>
+    <i r="3">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="2">
+      <x/>
+    </i>
+    <i r="3">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="2">
+      <x/>
+    </i>
+    <i r="3">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i r="2">
+      <x/>
+    </i>
+    <i r="3">
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="2">
+      <x v="1"/>
+    </i>
+    <i r="3">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="2">
+      <x v="1"/>
+    </i>
+    <i r="3">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="2">
+      <x v="1"/>
+    </i>
+    <i r="3">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i r="2">
+      <x v="1"/>
+    </i>
+    <i r="3">
+      <x/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="2">
+      <x v="2"/>
+    </i>
+    <i r="3">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="2">
+      <x v="2"/>
+    </i>
+    <i r="3">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="2">
+      <x v="2"/>
+    </i>
+    <i r="3">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i r="2">
+      <x v="2"/>
+    </i>
+    <i r="3">
+      <x/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i r="2">
+      <x v="3"/>
+    </i>
+    <i r="3">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i r="2">
+      <x v="3"/>
+    </i>
+    <i r="3">
+      <x/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <dataFields count="2">
+    <dataField name="Sum of Total Sales" fld="7" baseField="0" baseItem="0"/>
+    <dataField name="Sum of Units Sold" fld="5" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{551EE020-3337-4E06-A5B7-B01C4EA4033F}" name="PivotTable14" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A4:A5" firstHeaderRow="1" firstDataRow="1" firstDataCol="0" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="8">
+    <pivotField numFmtId="16" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="5">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="6">
+        <item x="4"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="2" hier="-1"/>
+    <pageField fld="3" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Sum of Total Sales" fld="7" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9D1F39A6-1B23-486F-93F5-31E6D9156815}" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:C20" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="8">
+    <pivotField numFmtId="16" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B1ACDBF9-6369-4E27-823C-6B3022FBB02F}" name="PivotTable3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="8">
+    <pivotField numFmtId="16" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0">
+      <items count="16">
+        <item x="13"/>
+        <item x="8"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="7"/>
+        <item x="12"/>
+        <item x="9"/>
+        <item x="4"/>
+        <item x="14"/>
+        <item x="6"/>
+        <item x="10"/>
+        <item x="5"/>
+        <item x="3"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Total Sales" fld="7" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E2B0A5A9-04BD-4B78-A5CC-79CAA69702C4}" name="PivotTable4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="8">
+    <pivotField numFmtId="16" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="6">
+        <item x="4"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Units Sold" fld="5" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9CC66B50-733C-4683-8320-20E6FBC3E63D}" name="PivotTable8" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:G9" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="8">
+    <pivotField numFmtId="16" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="6">
+        <item x="4"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0">
+      <items count="16">
+        <item x="13"/>
+        <item x="8"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="7"/>
+        <item x="12"/>
+        <item x="9"/>
+        <item x="4"/>
+        <item x="14"/>
+        <item x="6"/>
+        <item x="10"/>
+        <item x="5"/>
+        <item x="3"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="3"/>
+  </colFields>
+  <colItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Total Sales" fld="7" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4B8A74A4-57B2-440C-8014-39C7C40137FC}" name="PivotTable9" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="8">
+    <pivotField numFmtId="16" showAll="0">
+      <items count="16">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="6">
+        <item x="4"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Units Sold" fld="5" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F8F83277-9F81-49EE-A814-F1432FAE3057}" name="PivotTable10" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="8">
+    <pivotField numFmtId="16" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" measureFilter="1">
+      <items count="5">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0">
+      <items count="16">
+        <item x="13"/>
+        <item x="8"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="7"/>
+        <item x="12"/>
+        <item x="9"/>
+        <item x="4"/>
+        <item x="14"/>
+        <item x="6"/>
+        <item x="10"/>
+        <item x="5"/>
+        <item x="3"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Max of Total Sales" fld="7" subtotal="max" baseField="2" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="1">
+    <filter fld="2" type="count" evalOrder="-1" id="1" iMeasureFld="0">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <top10 val="10" filterVal="10"/>
+        </filterColumn>
+      </autoFilter>
+    </filter>
+  </filters>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BE7D98E2-E484-4516-AFD6-1129D742946F}" name="PivotTable11" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="8">
+    <pivotField numFmtId="16" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Total Sales" fld="7" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9D9176D1-2248-4D3B-81BA-89B0A52EB613}" name="PivotTable12" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:G9" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="8">
+    <pivotField numFmtId="16" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="6">
+        <item x="4"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="3"/>
+  </colFields>
+  <colItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Units Sold" fld="5" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8EF8ED01-5157-4D03-AB88-8A44B7B3718D}" name="PivotTable13" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:B6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="8">
+    <pivotField numFmtId="16" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of Unit Price" fld="6" subtotal="average" baseField="4" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9959,6 +15440,39 @@
 </table>
 </file>
 
+<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{03C2271C-4048-47F1-A7A9-D2FBD5EFD8A7}" name="Table15" displayName="Table15" ref="A196:G199" totalsRowShown="0">
+  <autoFilter ref="A196:G199" xr:uid="{03C2271C-4048-47F1-A7A9-D2FBD5EFD8A7}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{6FA3567B-9FC5-4D12-97AA-1C246CCAEB8D}" name="    Name"/>
+    <tableColumn id="2" xr3:uid="{B56742ED-04A9-4462-8C0F-C86153DD99FD}" name="HP"/>
+    <tableColumn id="3" xr3:uid="{19894410-0419-4CA6-B457-4A64F4ABC710}" name="Attack"/>
+    <tableColumn id="4" xr3:uid="{8DF64F29-0DCB-4ADE-9AE8-DDCF528A4F5A}" name="Defense"/>
+    <tableColumn id="5" xr3:uid="{6AF2FE62-60BB-4CC1-93FD-245559C425C8}" name="Sp. Atk"/>
+    <tableColumn id="6" xr3:uid="{BB60F1B3-CC3D-49CA-8EED-BC80FC1DB1F7}" name="Sp. Def"/>
+    <tableColumn id="7" xr3:uid="{57D7244D-9DCE-42C1-9F1D-0C83C61253B1}" name="Speed"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{C878C128-E01A-4729-B9B1-B81176607026}" name="Table16" displayName="Table16" ref="A226:H241" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
+  <autoFilter ref="A226:H241" xr:uid="{C878C128-E01A-4729-B9B1-B81176607026}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{EA082774-4A2A-410F-B9EF-F28AE953503A}" name="Date" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{57DCB296-E325-4BED-A044-03510F4D86E0}" name="Salesperson" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{8934067F-64B1-4345-95EC-47D19036A135}" name="Region" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{36DF0F8F-2D0A-45CE-8D39-82D07DAD91A3}" name="Product" dataDxfId="16"/>
+    <tableColumn id="5" xr3:uid="{3664072A-5AA9-45E2-910C-1BF58D17263A}" name="Category" dataDxfId="15"/>
+    <tableColumn id="6" xr3:uid="{2887507F-CB2B-40FC-8340-FA14C24877DD}" name="Units Sold" dataDxfId="14"/>
+    <tableColumn id="7" xr3:uid="{F8015508-001F-45A9-B6C2-1C34C54AFC36}" name="Unit Price" dataDxfId="13"/>
+    <tableColumn id="8" xr3:uid="{40EB56A3-89ED-4163-A4FA-66E41A953094}" name="Total Sales" dataDxfId="12"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6B87212E-8006-434D-9CBC-67463F1B3E39}" name="Table2" displayName="Table2" ref="A13:H21" totalsRowShown="0">
   <autoFilter ref="A13:H21" xr:uid="{6B87212E-8006-434D-9CBC-67463F1B3E39}"/>
@@ -9982,7 +15496,7 @@
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{97E23F36-17CA-4C33-B793-2A3D150D48ED}" name="      Name"/>
     <tableColumn id="2" xr3:uid="{D3C49F1C-1B57-4825-8B6F-2A231D9E8135}" name="Type 1"/>
-    <tableColumn id="3" xr3:uid="{9BB1CF94-5896-40AB-9160-B9CBF63EC108}" name="Birthday" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{9BB1CF94-5896-40AB-9160-B9CBF63EC108}" name="Birthday" dataDxfId="22"/>
     <tableColumn id="4" xr3:uid="{CB18B56D-058A-456E-85A7-FFB66EB48067}" name="Year"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -10370,14 +15884,742 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE6C1AF8-9245-473D-AD13-9AAB32511957}">
+  <dimension ref="A4:C51"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="B4" t="s">
+        <v>163</v>
+      </c>
+      <c r="C4" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="B5">
+        <v>104200</v>
+      </c>
+      <c r="C5">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="B6">
+        <v>11200</v>
+      </c>
+      <c r="C6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="B7">
+        <v>11200</v>
+      </c>
+      <c r="C7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="B8">
+        <v>11200</v>
+      </c>
+      <c r="C8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="B9">
+        <v>6000</v>
+      </c>
+      <c r="C9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="B10">
+        <v>6000</v>
+      </c>
+      <c r="C10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="B11">
+        <v>6000</v>
+      </c>
+      <c r="C11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="B12">
+        <v>51000</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="B13">
+        <v>51000</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="B14">
+        <v>51000</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="B15">
+        <v>36000</v>
+      </c>
+      <c r="C15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="B16">
+        <v>36000</v>
+      </c>
+      <c r="C16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="B17">
+        <v>36000</v>
+      </c>
+      <c r="C17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="B18">
+        <v>70500</v>
+      </c>
+      <c r="C18">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="B19">
+        <v>9600</v>
+      </c>
+      <c r="C19">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="B20">
+        <v>9600</v>
+      </c>
+      <c r="C20">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="B21">
+        <v>9600</v>
+      </c>
+      <c r="C21">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="B22">
+        <v>3900</v>
+      </c>
+      <c r="C22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="B23">
+        <v>3900</v>
+      </c>
+      <c r="C23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="B24">
+        <v>3900</v>
+      </c>
+      <c r="C24">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="B25">
+        <v>52000</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="B26">
+        <v>52000</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="B27">
+        <v>52000</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="B28">
+        <v>5000</v>
+      </c>
+      <c r="C28">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="B29">
+        <v>5000</v>
+      </c>
+      <c r="C29">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="B30">
+        <v>5000</v>
+      </c>
+      <c r="C30">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="B31">
+        <v>122900</v>
+      </c>
+      <c r="C31">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="B32">
+        <v>10500</v>
+      </c>
+      <c r="C32">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="B33">
+        <v>10500</v>
+      </c>
+      <c r="C33">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="B34">
+        <v>10500</v>
+      </c>
+      <c r="C34">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="B35">
+        <v>4400</v>
+      </c>
+      <c r="C35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="B36">
+        <v>4400</v>
+      </c>
+      <c r="C36">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="B37">
+        <v>4400</v>
+      </c>
+      <c r="C37">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="B38">
+        <v>100000</v>
+      </c>
+      <c r="C38">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="B39">
+        <v>100000</v>
+      </c>
+      <c r="C39">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="B40">
+        <v>100000</v>
+      </c>
+      <c r="C40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="B41">
+        <v>8000</v>
+      </c>
+      <c r="C41">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="B42">
+        <v>8000</v>
+      </c>
+      <c r="C42">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="B43">
+        <v>8000</v>
+      </c>
+      <c r="C43">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="B44">
+        <v>150750</v>
+      </c>
+      <c r="C44">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="B45">
+        <v>144000</v>
+      </c>
+      <c r="C45">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="B46">
+        <v>144000</v>
+      </c>
+      <c r="C46">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="B47">
+        <v>144000</v>
+      </c>
+      <c r="C47">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="B48">
+        <v>6750</v>
+      </c>
+      <c r="C48">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="B49">
+        <v>6750</v>
+      </c>
+      <c r="C49">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="B50">
+        <v>6750</v>
+      </c>
+      <c r="C50">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="B51">
+        <v>448350</v>
+      </c>
+      <c r="C51">
+        <v>91</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7141577F-7403-4678-9A7D-59D2004D2339}">
+  <dimension ref="A1:I7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="23.4" x14ac:dyDescent="0.45">
+      <c r="A1" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="B1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="B2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D3" s="16" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="23.4" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D4" s="18"/>
+      <c r="H4" s="13"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>448350</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D6" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D7" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7DF161C-80DE-4F5F-AC23-BA966817E11A}">
+  <dimension ref="A3:C20"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="20"/>
+      <c r="B3" s="21"/>
+      <c r="C3" s="22"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="23"/>
+      <c r="B4" s="24"/>
+      <c r="C4" s="25"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="23"/>
+      <c r="B5" s="24"/>
+      <c r="C5" s="25"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="23"/>
+      <c r="B6" s="24"/>
+      <c r="C6" s="25"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="23"/>
+      <c r="B7" s="24"/>
+      <c r="C7" s="25"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="23"/>
+      <c r="B8" s="24"/>
+      <c r="C8" s="25"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="23"/>
+      <c r="B9" s="24"/>
+      <c r="C9" s="25"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="23"/>
+      <c r="B10" s="24"/>
+      <c r="C10" s="25"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="23"/>
+      <c r="B11" s="24"/>
+      <c r="C11" s="25"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="23"/>
+      <c r="B12" s="24"/>
+      <c r="C12" s="25"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="23"/>
+      <c r="B13" s="24"/>
+      <c r="C13" s="25"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="23"/>
+      <c r="B14" s="24"/>
+      <c r="C14" s="25"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="23"/>
+      <c r="B15" s="24"/>
+      <c r="C15" s="25"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="23"/>
+      <c r="B16" s="24"/>
+      <c r="C16" s="25"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="23"/>
+      <c r="B17" s="24"/>
+      <c r="C17" s="25"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="23"/>
+      <c r="B18" s="24"/>
+      <c r="C18" s="25"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="23"/>
+      <c r="B19" s="24"/>
+      <c r="C19" s="25"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="26"/>
+      <c r="B20" s="27"/>
+      <c r="C20" s="28"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E6FF592-C761-4D6E-9620-83C6964B02BC}">
-  <dimension ref="A1:P192"/>
+  <dimension ref="A1:P241"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.44140625" customWidth="1"/>
-    <col min="2" max="2" width="12.77734375" customWidth="1"/>
+    <col min="2" max="2" width="13.44140625" customWidth="1"/>
     <col min="3" max="3" width="13.21875" customWidth="1"/>
-    <col min="4" max="5" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="9.77734375" customWidth="1"/>
+    <col min="5" max="5" width="10.77734375" customWidth="1"/>
+    <col min="6" max="6" width="11.77734375" customWidth="1"/>
+    <col min="7" max="7" width="11.44140625" customWidth="1"/>
+    <col min="8" max="8" width="12.21875" customWidth="1"/>
     <col min="9" max="9" width="10.44140625" customWidth="1"/>
     <col min="11" max="11" width="11.44140625" customWidth="1"/>
     <col min="12" max="13" width="10.44140625" customWidth="1"/>
@@ -12800,6 +19042,529 @@
       </c>
       <c r="I192" s="2" t="s">
         <v>118</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A196" t="s">
+        <v>107</v>
+      </c>
+      <c r="B196" t="s">
+        <v>2</v>
+      </c>
+      <c r="C196" t="s">
+        <v>3</v>
+      </c>
+      <c r="D196" t="s">
+        <v>4</v>
+      </c>
+      <c r="E196" t="s">
+        <v>5</v>
+      </c>
+      <c r="F196" t="s">
+        <v>6</v>
+      </c>
+      <c r="G196" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A197" t="s">
+        <v>133</v>
+      </c>
+      <c r="B197">
+        <v>45</v>
+      </c>
+      <c r="C197">
+        <v>49</v>
+      </c>
+      <c r="D197">
+        <v>49</v>
+      </c>
+      <c r="E197">
+        <v>65</v>
+      </c>
+      <c r="F197">
+        <v>65</v>
+      </c>
+      <c r="G197">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A198" t="s">
+        <v>134</v>
+      </c>
+      <c r="B198">
+        <v>39</v>
+      </c>
+      <c r="C198">
+        <v>52</v>
+      </c>
+      <c r="D198">
+        <v>43</v>
+      </c>
+      <c r="E198">
+        <v>60</v>
+      </c>
+      <c r="F198">
+        <v>50</v>
+      </c>
+      <c r="G198">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A199" t="s">
+        <v>135</v>
+      </c>
+      <c r="B199">
+        <v>44</v>
+      </c>
+      <c r="C199">
+        <v>48</v>
+      </c>
+      <c r="D199">
+        <v>65</v>
+      </c>
+      <c r="E199">
+        <v>50</v>
+      </c>
+      <c r="F199">
+        <v>64</v>
+      </c>
+      <c r="G199">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A200" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="222" spans="5:8" ht="33" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="G222" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="H222" s="4"/>
+    </row>
+    <row r="223" spans="5:8" ht="16.8" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="224" spans="5:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E224" s="5"/>
+    </row>
+    <row r="226" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A226" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="B226" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="C226" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="D226" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="E226" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="F226" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="G226" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="H226" s="6" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A227" s="7">
+        <v>46023</v>
+      </c>
+      <c r="B227" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C227" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D227" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E227" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F227" s="3">
+        <v>2</v>
+      </c>
+      <c r="G227" s="3">
+        <v>50000</v>
+      </c>
+      <c r="H227" s="3">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A228" s="7">
+        <v>46024</v>
+      </c>
+      <c r="B228" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C228" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D228" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E228" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="F228" s="3">
+        <v>10</v>
+      </c>
+      <c r="G228" s="3">
+        <v>500</v>
+      </c>
+      <c r="H228" s="3">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A229" s="7">
+        <v>46025</v>
+      </c>
+      <c r="B229" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C229" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D229" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="E229" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="F229" s="3">
+        <v>5</v>
+      </c>
+      <c r="G229" s="3">
+        <v>1200</v>
+      </c>
+      <c r="H229" s="3">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A230" s="7">
+        <v>46026</v>
+      </c>
+      <c r="B230" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C230" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D230" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="E230" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F230" s="3">
+        <v>3</v>
+      </c>
+      <c r="G230" s="3">
+        <v>20000</v>
+      </c>
+      <c r="H230" s="3">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="231" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A231" s="7">
+        <v>46027</v>
+      </c>
+      <c r="B231" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C231" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D231" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="E231" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="F231" s="3">
+        <v>7</v>
+      </c>
+      <c r="G231" s="3">
+        <v>1500</v>
+      </c>
+      <c r="H231" s="3">
+        <v>10500</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A232" s="7">
+        <v>46028</v>
+      </c>
+      <c r="B232" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C232" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D232" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E232" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F232" s="3">
+        <v>1</v>
+      </c>
+      <c r="G232" s="3">
+        <v>52000</v>
+      </c>
+      <c r="H232" s="3">
+        <v>52000</v>
+      </c>
+    </row>
+    <row r="233" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A233" s="7">
+        <v>46029</v>
+      </c>
+      <c r="B233" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C233" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D233" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="E233" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F233" s="3">
+        <v>2</v>
+      </c>
+      <c r="G233" s="3">
+        <v>18000</v>
+      </c>
+      <c r="H233" s="3">
+        <v>36000</v>
+      </c>
+    </row>
+    <row r="234" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A234" s="7">
+        <v>46030</v>
+      </c>
+      <c r="B234" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C234" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D234" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E234" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="F234" s="3">
+        <v>15</v>
+      </c>
+      <c r="G234" s="3">
+        <v>450</v>
+      </c>
+      <c r="H234" s="3">
+        <v>6750</v>
+      </c>
+    </row>
+    <row r="235" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A235" s="7">
+        <v>46031</v>
+      </c>
+      <c r="B235" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C235" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D235" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="E235" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="F235" s="3">
+        <v>4</v>
+      </c>
+      <c r="G235" s="3">
+        <v>1100</v>
+      </c>
+      <c r="H235" s="3">
+        <v>4400</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A236" s="7">
+        <v>46032</v>
+      </c>
+      <c r="B236" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C236" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D236" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="E236" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="F236" s="3">
+        <v>6</v>
+      </c>
+      <c r="G236" s="3">
+        <v>1600</v>
+      </c>
+      <c r="H236" s="3">
+        <v>9600</v>
+      </c>
+    </row>
+    <row r="237" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A237" s="7">
+        <v>46033</v>
+      </c>
+      <c r="B237" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C237" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D237" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E237" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F237" s="3">
+        <v>1</v>
+      </c>
+      <c r="G237" s="3">
+        <v>51000</v>
+      </c>
+      <c r="H237" s="3">
+        <v>51000</v>
+      </c>
+    </row>
+    <row r="238" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A238" s="7">
+        <v>46034</v>
+      </c>
+      <c r="B238" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C238" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D238" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="E238" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F238" s="3">
+        <v>4</v>
+      </c>
+      <c r="G238" s="3">
+        <v>21000</v>
+      </c>
+      <c r="H238" s="3">
+        <v>84000</v>
+      </c>
+    </row>
+    <row r="239" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A239" s="7">
+        <v>46035</v>
+      </c>
+      <c r="B239" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C239" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D239" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E239" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="F239" s="3">
+        <v>20</v>
+      </c>
+      <c r="G239" s="3">
+        <v>400</v>
+      </c>
+      <c r="H239" s="3">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="240" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A240" s="7">
+        <v>46036</v>
+      </c>
+      <c r="B240" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C240" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D240" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="E240" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="F240" s="3">
+        <v>3</v>
+      </c>
+      <c r="G240" s="3">
+        <v>1300</v>
+      </c>
+      <c r="H240" s="3">
+        <v>3900</v>
+      </c>
+    </row>
+    <row r="241" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A241" s="7">
+        <v>46037</v>
+      </c>
+      <c r="B241" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C241" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D241" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="E241" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="F241" s="3">
+        <v>8</v>
+      </c>
+      <c r="G241" s="3">
+        <v>1400</v>
+      </c>
+      <c r="H241" s="3">
+        <v>11200</v>
       </c>
     </row>
   </sheetData>
@@ -12884,7 +19649,7 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
-  <tableParts count="14">
+  <tableParts count="16">
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
     <tablePart r:id="rId4"/>
@@ -12899,6 +19664,8 @@
     <tablePart r:id="rId13"/>
     <tablePart r:id="rId14"/>
     <tablePart r:id="rId15"/>
+    <tablePart r:id="rId16"/>
+    <tablePart r:id="rId17"/>
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -12920,4 +19687,723 @@
     </ext>
   </extLst>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0DE4D03-843E-466F-94A1-6A24EA2DD8DD}">
+  <dimension ref="A3:B8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="B3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="B4">
+        <v>104200</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="B5">
+        <v>70500</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="B6">
+        <v>122900</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="B7">
+        <v>150750</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="B8">
+        <v>448350</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22633FC6-50F3-4E25-BE34-4AB55020464C}">
+  <dimension ref="A3:B9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="B3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B4">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="B5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="B7">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="B8">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="B9">
+        <v>91</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AAC02D0-299B-4FAE-9A5B-C4DB4823C040}">
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
+      <c r="B1" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="C1" s="15"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="B4" t="s">
+        <v>159</v>
+      </c>
+      <c r="C4" t="s">
+        <v>155</v>
+      </c>
+      <c r="D4" t="s">
+        <v>147</v>
+      </c>
+      <c r="E4" t="s">
+        <v>158</v>
+      </c>
+      <c r="F4" t="s">
+        <v>151</v>
+      </c>
+      <c r="G4" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="B5">
+        <v>11200</v>
+      </c>
+      <c r="C5">
+        <v>6000</v>
+      </c>
+      <c r="D5">
+        <v>51000</v>
+      </c>
+      <c r="E5">
+        <v>36000</v>
+      </c>
+      <c r="G5">
+        <v>104200</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="B6">
+        <v>9600</v>
+      </c>
+      <c r="C6">
+        <v>3900</v>
+      </c>
+      <c r="D6">
+        <v>52000</v>
+      </c>
+      <c r="F6">
+        <v>5000</v>
+      </c>
+      <c r="G6">
+        <v>70500</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="B7">
+        <v>10500</v>
+      </c>
+      <c r="C7">
+        <v>4400</v>
+      </c>
+      <c r="D7">
+        <v>100000</v>
+      </c>
+      <c r="F7">
+        <v>8000</v>
+      </c>
+      <c r="G7">
+        <v>122900</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="E8">
+        <v>144000</v>
+      </c>
+      <c r="F8">
+        <v>6750</v>
+      </c>
+      <c r="G8">
+        <v>150750</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="B9">
+        <v>31300</v>
+      </c>
+      <c r="C9">
+        <v>14300</v>
+      </c>
+      <c r="D9">
+        <v>203000</v>
+      </c>
+      <c r="E9">
+        <v>180000</v>
+      </c>
+      <c r="F9">
+        <v>19750</v>
+      </c>
+      <c r="G9">
+        <v>448350</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
+      <c r="B12" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D14" s="14"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4374244E-0F90-40A6-B0A9-C18DEDBA0C5C}">
+  <dimension ref="A2:F9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:6" ht="23.4" x14ac:dyDescent="0.45">
+      <c r="C2" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="17"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="B3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B4">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="B5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="B7">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="B8">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="B9">
+        <v>91</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90134A55-9960-414A-9AFF-4669A7C84271}">
+  <dimension ref="A2:G8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
+      <c r="C2" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="B3" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="B4">
+        <v>51000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="B5">
+        <v>52000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="B6">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="B7">
+        <v>84000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="B8">
+        <v>100000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7A77137-3B33-4D44-BBCB-27AF260EEA4F}">
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
+      <c r="C1" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="B3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="B4">
+        <v>104200</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="B5">
+        <v>70500</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="B6">
+        <v>122900</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="B7">
+        <v>150750</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="B8">
+        <v>448350</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A86FD954-72BF-427C-B542-F1AE7471EE4D}">
+  <dimension ref="A2:H9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:8" ht="23.4" x14ac:dyDescent="0.45">
+      <c r="C2" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="B4" t="s">
+        <v>159</v>
+      </c>
+      <c r="C4" t="s">
+        <v>155</v>
+      </c>
+      <c r="D4" t="s">
+        <v>147</v>
+      </c>
+      <c r="E4" t="s">
+        <v>158</v>
+      </c>
+      <c r="F4" t="s">
+        <v>151</v>
+      </c>
+      <c r="G4" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="B5">
+        <v>8</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="B6">
+        <v>6</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>10</v>
+      </c>
+      <c r="G6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="B7">
+        <v>7</v>
+      </c>
+      <c r="C7">
+        <v>4</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>20</v>
+      </c>
+      <c r="G7">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="E8">
+        <v>7</v>
+      </c>
+      <c r="F8">
+        <v>15</v>
+      </c>
+      <c r="G8">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="B9">
+        <v>21</v>
+      </c>
+      <c r="C9">
+        <v>12</v>
+      </c>
+      <c r="D9">
+        <v>4</v>
+      </c>
+      <c r="E9">
+        <v>9</v>
+      </c>
+      <c r="F9">
+        <v>45</v>
+      </c>
+      <c r="G9">
+        <v>91</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9AABB59-48F1-4050-83BF-EEE2CBD7F084}">
+  <dimension ref="A3:B6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="B3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="B4">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="B5">
+        <v>35333.333333333336</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="B6">
+        <v>14763.333333333334</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>